--- a/meta/Chap1_NCT_16S_metadata.xlsx
+++ b/meta/Chap1_NCT_16S_metadata.xlsx
@@ -10215,7 +10215,7 @@
   <dimension ref="A1:H380"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="47.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="49.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="8.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23.29"/>
